--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,116 +21482,116 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ107" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO107" t="n">
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ107" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR107" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS107" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT107" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY107" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ107" t="n">
         <v>0</v>
@@ -21600,19 +21600,19 @@
         <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,116 +21876,116 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL109" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN109" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO109" t="n">
         <v>0</v>
       </c>
       <c r="AP109" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR109" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS109" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU109" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW109" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY109" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ109" t="n">
         <v>0</v>
@@ -21994,19 +21994,19 @@
         <v>0</v>
       </c>
       <c r="BB109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF109" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF146" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30205,10 +30205,10 @@
         <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH151" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF185" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF186" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,22 +40350,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,22 +40547,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="Q220" t="n">
-        <v>4.88</v>
+        <v>3.76</v>
       </c>
       <c r="R220" t="n">
-        <v>7.06</v>
+        <v>4.17</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,10 +43792,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="AF220" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.78</v>
+        <v>4.88</v>
       </c>
       <c r="R221" t="n">
-        <v>2.05</v>
+        <v>7.06</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43989,10 +43989,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AF221" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="R222" t="n">
-        <v>4.17</v>
+        <v>2.05</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AF222" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44586,10 +44586,10 @@
         <v>0</v>
       </c>
       <c r="AG224" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH224" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI224" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,22 +49412,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,22 +51382,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,22 +51776,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53400,13 +53400,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q269" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,22 +53943,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55519,22 +55519,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,22 +55716,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q282" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,10 +56006,10 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF282" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG282" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q287" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57143,13 +57143,13 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q288" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R288" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S288" t="n">
         <v>0</v>
@@ -57188,10 +57188,10 @@
         <v>0</v>
       </c>
       <c r="AE288" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF288" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG288" t="n">
         <v>0</v>
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,22 +57489,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,22 +59459,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59853,22 +59853,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60838,22 +60838,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61050,7 +61050,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,22 +61429,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,22 +61626,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,22 +61823,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,7 +62020,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q319" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63295,10 +63295,10 @@
         <v>0</v>
       </c>
       <c r="AE319" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF319" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG319" t="n">
         <v>0</v>
@@ -63399,7 +63399,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -63409,12 +63409,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -63447,13 +63447,13 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q320" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R320" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
@@ -63492,10 +63492,10 @@
         <v>0</v>
       </c>
       <c r="AE320" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF320" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG320" t="n">
         <v>0</v>
@@ -63793,7 +63793,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63990,7 +63990,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -64000,12 +64000,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -65576,12 +65576,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -65614,13 +65614,13 @@
         </is>
       </c>
       <c r="P331" t="n">
-        <v>3.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q331" t="n">
-        <v>3.4</v>
+        <v>4.76</v>
       </c>
       <c r="R331" t="n">
-        <v>2.22</v>
+        <v>9.1</v>
       </c>
       <c r="S331" t="n">
         <v>0</v>
@@ -65659,10 +65659,10 @@
         <v>0</v>
       </c>
       <c r="AE331" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF331" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG331" t="n">
         <v>0</v>
@@ -65773,12 +65773,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -65811,13 +65811,13 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>1.39</v>
+        <v>3.36</v>
       </c>
       <c r="Q332" t="n">
-        <v>4.76</v>
+        <v>3.4</v>
       </c>
       <c r="R332" t="n">
-        <v>9.1</v>
+        <v>2.22</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -65856,10 +65856,10 @@
         <v>0</v>
       </c>
       <c r="AE332" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF332" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG332" t="n">
         <v>0</v>
@@ -66157,7 +66157,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -66167,12 +66167,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -66364,12 +66364,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -66551,7 +66551,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -66561,12 +66561,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -66748,7 +66748,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -66758,12 +66758,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -66945,7 +66945,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -66955,12 +66955,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G338" t="n">

--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,116 +21482,116 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ107" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO107" t="n">
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ107" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR107" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS107" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT107" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY107" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ107" t="n">
         <v>0</v>
@@ -21600,19 +21600,19 @@
         <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,116 +22467,116 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI112" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK112" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL112" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM112" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN112" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO112" t="n">
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR112" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS112" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU112" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW112" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX112" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ112" t="n">
         <v>0</v>
@@ -22585,19 +22585,19 @@
         <v>0</v>
       </c>
       <c r="BB112" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC112" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD112" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE112" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF112" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35912,10 +35912,10 @@
         <v>0</v>
       </c>
       <c r="AE180" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF180" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF181" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.99</v>
+        <v>5.53</v>
       </c>
       <c r="R190" t="n">
-        <v>3.49</v>
+        <v>6.75</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF190" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,22 +40350,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="Q222" t="n">
-        <v>4.88</v>
+        <v>3.76</v>
       </c>
       <c r="R222" t="n">
-        <v>7.06</v>
+        <v>4.17</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="AF222" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.76</v>
+        <v>4.88</v>
       </c>
       <c r="R224" t="n">
-        <v>4.17</v>
+        <v>7.06</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.99</v>
+        <v>1.63</v>
       </c>
       <c r="AF224" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q226" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44980,10 +44980,10 @@
         <v>0</v>
       </c>
       <c r="AG226" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH226" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI226" t="n">
         <v>0</v>
@@ -45078,22 +45078,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q228" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45374,10 +45374,10 @@
         <v>0</v>
       </c>
       <c r="AG228" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51579,22 +51579,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -53943,22 +53943,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q276" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="Q282" t="n">
-        <v>4.98</v>
+        <v>3.53</v>
       </c>
       <c r="R282" t="n">
-        <v>5.99</v>
+        <v>2.54</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,16 +56006,16 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF282" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG282" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH282" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.53</v>
+        <v>4.98</v>
       </c>
       <c r="R283" t="n">
-        <v>2.54</v>
+        <v>5.99</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,16 +56203,16 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG283" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH283" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q286" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56794,10 +56794,10 @@
         <v>0</v>
       </c>
       <c r="AE286" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF286" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG286" t="n">
         <v>0</v>
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q287" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -56991,10 +56991,10 @@
         <v>0</v>
       </c>
       <c r="AE287" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF287" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG287" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58080,22 +58080,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,7 +60060,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -60247,22 +60247,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60454,7 +60454,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61035,22 +61035,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61439,7 +61439,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62217,22 +62217,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,7 +62414,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -62424,12 +62424,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62808,22 +62808,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64975,7 +64975,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -64985,12 +64985,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -65172,7 +65172,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -65182,12 +65182,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -65220,13 +65220,13 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q329" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R329" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S329" t="n">
         <v>0</v>
@@ -65265,10 +65265,10 @@
         <v>0</v>
       </c>
       <c r="AE329" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF329" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG329" t="n">
         <v>0</v>
@@ -65369,7 +65369,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -65379,12 +65379,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -65417,13 +65417,13 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q330" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R330" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S330" t="n">
         <v>0</v>
@@ -65462,10 +65462,10 @@
         <v>0</v>
       </c>
       <c r="AE330" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF330" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG330" t="n">
         <v>0</v>
@@ -65773,12 +65773,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -65811,13 +65811,13 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>1.39</v>
+        <v>3.36</v>
       </c>
       <c r="Q332" t="n">
-        <v>4.76</v>
+        <v>3.4</v>
       </c>
       <c r="R332" t="n">
-        <v>9.1</v>
+        <v>2.22</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -65856,10 +65856,10 @@
         <v>0</v>
       </c>
       <c r="AE332" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF332" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG332" t="n">
         <v>0</v>
@@ -65960,7 +65960,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -65970,12 +65970,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -66157,7 +66157,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -66167,12 +66167,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -66205,13 +66205,13 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q334" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R334" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -66354,7 +66354,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -66364,12 +66364,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -66551,7 +66551,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -66561,12 +66561,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -66599,13 +66599,13 @@
         </is>
       </c>
       <c r="P336" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q336" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R336" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S336" t="n">
         <v>0</v>
@@ -66644,10 +66644,10 @@
         <v>0</v>
       </c>
       <c r="AE336" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF336" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG336" t="n">
         <v>0</v>
@@ -66748,7 +66748,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -66758,12 +66758,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -66945,7 +66945,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -66955,12 +66955,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -67142,7 +67142,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -67349,12 +67349,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -67536,7 +67536,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -67546,12 +67546,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G341" t="n">

--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,116 +21876,116 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL109" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN109" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO109" t="n">
         <v>0</v>
       </c>
       <c r="AP109" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR109" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS109" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU109" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW109" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY109" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ109" t="n">
         <v>0</v>
@@ -21994,19 +21994,19 @@
         <v>0</v>
       </c>
       <c r="BB109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF109" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,116 +22467,116 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL112" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM112" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN112" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO112" t="n">
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR112" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS112" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT112" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU112" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV112" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW112" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX112" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY112" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ112" t="n">
         <v>0</v>
@@ -22585,19 +22585,19 @@
         <v>0</v>
       </c>
       <c r="BB112" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE112" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF112" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF182" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF190" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,22 +40547,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,22 +43699,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,22 +43896,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH225" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q226" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44980,10 +44980,10 @@
         <v>0</v>
       </c>
       <c r="AG226" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI226" t="n">
         <v>0</v>
@@ -45078,22 +45078,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q240" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="Q282" t="n">
-        <v>3.53</v>
+        <v>4.98</v>
       </c>
       <c r="R282" t="n">
-        <v>2.54</v>
+        <v>5.99</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,16 +56006,16 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF282" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG282" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH282" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="Q283" t="n">
-        <v>4.98</v>
+        <v>3.53</v>
       </c>
       <c r="R283" t="n">
-        <v>5.99</v>
+        <v>2.54</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,16 +56203,16 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF283" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG283" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH283" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56504,22 +56504,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q286" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56794,10 +56794,10 @@
         <v>0</v>
       </c>
       <c r="AE286" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF286" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG286" t="n">
         <v>0</v>
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57340,13 +57340,13 @@
         </is>
       </c>
       <c r="P289" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q289" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R289" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
@@ -57489,22 +57489,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q294" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58370,10 +58370,10 @@
         <v>0</v>
       </c>
       <c r="AE294" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF294" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG294" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60247,22 +60247,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,22 +62020,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62414,7 +62414,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -62424,12 +62424,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62611,22 +62611,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,22 +62808,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64778,7 +64778,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -64788,12 +64788,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -65763,7 +65763,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -65773,12 +65773,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -65811,13 +65811,13 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q332" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R332" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -65856,10 +65856,10 @@
         <v>0</v>
       </c>
       <c r="AE332" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF332" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG332" t="n">
         <v>0</v>
@@ -65970,12 +65970,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -66364,12 +66364,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -66402,13 +66402,13 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q335" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R335" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S335" t="n">
         <v>0</v>
@@ -66447,10 +66447,10 @@
         <v>0</v>
       </c>
       <c r="AE335" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF335" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG335" t="n">
         <v>0</v>
@@ -66551,7 +66551,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -66561,12 +66561,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -66945,7 +66945,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -66955,12 +66955,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -67142,7 +67142,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -67349,12 +67349,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -67536,7 +67536,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -67546,12 +67546,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G341" t="n">

--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.44</v>
+        <v>2.37</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>2.1</v>
+        <v>2.91</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19370,10 +19370,10 @@
         <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,116 +21876,116 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD109" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI109" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL109" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO109" t="n">
         <v>0</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS109" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT109" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV109" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW109" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX109" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY109" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ109" t="n">
         <v>0</v>
@@ -21994,19 +21994,19 @@
         <v>0</v>
       </c>
       <c r="BB109" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE109" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF109" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23649,116 +23649,116 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD118" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG118" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH118" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI118" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK118" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL118" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM118" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN118" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO118" t="n">
         <v>0</v>
       </c>
       <c r="AP118" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR118" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS118" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU118" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV118" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW118" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX118" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY118" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ118" t="n">
         <v>0</v>
@@ -23767,19 +23767,19 @@
         <v>0</v>
       </c>
       <c r="BB118" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC118" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD118" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE118" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF118" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG118" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF146" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.99</v>
+        <v>5.53</v>
       </c>
       <c r="R181" t="n">
-        <v>3.49</v>
+        <v>6.75</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF181" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF182" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF189" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,22 +39956,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,22 +40547,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,22 +43896,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q221" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.76</v>
+        <v>4.88</v>
       </c>
       <c r="R222" t="n">
-        <v>4.17</v>
+        <v>7.06</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.99</v>
+        <v>1.63</v>
       </c>
       <c r="AF222" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="Q224" t="n">
-        <v>4.88</v>
+        <v>3.76</v>
       </c>
       <c r="R224" t="n">
-        <v>7.06</v>
+        <v>4.17</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="AF224" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q227" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH231" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF243" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF257" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51579,22 +51579,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="Q282" t="n">
-        <v>4.98</v>
+        <v>3.53</v>
       </c>
       <c r="R282" t="n">
-        <v>5.99</v>
+        <v>2.54</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,16 +56006,16 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF282" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG282" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH282" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.53</v>
+        <v>4.98</v>
       </c>
       <c r="R283" t="n">
-        <v>2.54</v>
+        <v>5.99</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,16 +56203,16 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG283" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH283" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI283" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56504,22 +56504,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q286" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56794,10 +56794,10 @@
         <v>0</v>
       </c>
       <c r="AE286" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF286" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG286" t="n">
         <v>0</v>
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57340,13 +57340,13 @@
         </is>
       </c>
       <c r="P289" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q289" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
@@ -57489,22 +57489,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,22 +57883,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q294" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58370,10 +58370,10 @@
         <v>0</v>
       </c>
       <c r="AE294" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF294" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG294" t="n">
         <v>0</v>
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59853,22 +59853,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60853,7 +60853,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61050,7 +61050,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,22 +62020,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62217,22 +62217,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62611,22 +62611,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,7 +62808,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64581,7 +64581,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -64591,12 +64591,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -64778,7 +64778,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -64788,12 +64788,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -64975,7 +64975,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -64985,12 +64985,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -65763,7 +65763,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -65773,12 +65773,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -65960,7 +65960,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -65970,12 +65970,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -66008,13 +66008,13 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q333" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R333" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="S333" t="n">
         <v>0</v>
@@ -66167,12 +66167,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -66205,13 +66205,13 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>1.39</v>
+        <v>3.36</v>
       </c>
       <c r="Q334" t="n">
-        <v>4.76</v>
+        <v>3.4</v>
       </c>
       <c r="R334" t="n">
-        <v>9.1</v>
+        <v>2.22</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -66250,10 +66250,10 @@
         <v>0</v>
       </c>
       <c r="AE334" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF334" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG334" t="n">
         <v>0</v>
@@ -66354,7 +66354,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -66364,12 +66364,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -66402,13 +66402,13 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q335" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R335" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S335" t="n">
         <v>0</v>
@@ -66447,10 +66447,10 @@
         <v>0</v>
       </c>
       <c r="AE335" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF335" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG335" t="n">
         <v>0</v>
@@ -66551,7 +66551,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -66561,12 +66561,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -67349,12 +67349,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G340" t="n">

--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>2.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="R96" t="n">
-        <v>4.35</v>
+        <v>2.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19370,10 +19370,10 @@
         <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.14</v>
+        <v>8.35</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.72</v>
+        <v>5.38</v>
       </c>
       <c r="R99" t="n">
-        <v>2.99</v>
+        <v>1.31</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>8.35</v>
+        <v>2.27</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.38</v>
+        <v>3.25</v>
       </c>
       <c r="R105" t="n">
-        <v>1.31</v>
+        <v>3.13</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,116 +21679,116 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK108" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM108" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN108" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO108" t="n">
         <v>0</v>
       </c>
       <c r="AP108" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR108" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS108" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU108" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV108" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW108" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX108" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY108" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ108" t="n">
         <v>0</v>
@@ -21797,19 +21797,19 @@
         <v>0</v>
       </c>
       <c r="BB108" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE108" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF108" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.23</v>
+        <v>3.62</v>
       </c>
       <c r="R112" t="n">
-        <v>2.29</v>
+        <v>3.35</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="R114" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23649,116 +23649,116 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK118" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL118" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM118" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN118" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO118" t="n">
         <v>0</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ118" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR118" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS118" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT118" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV118" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW118" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX118" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY118" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ118" t="n">
         <v>0</v>
@@ -23767,19 +23767,19 @@
         <v>0</v>
       </c>
       <c r="BB118" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE118" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF118" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25225,17 +25225,17 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.58</v>
+        <v>3.19</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="R146" t="n">
-        <v>4.95</v>
+        <v>2.31</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>5.21</v>
+        <v>2.27</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.68</v>
+        <v>3.24</v>
       </c>
       <c r="R148" t="n">
-        <v>1.81</v>
+        <v>3.06</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF148" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R149" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,22 +33061,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="R173" t="n">
-        <v>4.2</v>
+        <v>2.18</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="Q181" t="n">
-        <v>5.53</v>
+        <v>3.99</v>
       </c>
       <c r="R181" t="n">
-        <v>6.75</v>
+        <v>3.49</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF181" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF189" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,22 +39956,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,22 +40153,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="R213" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF213" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.97</v>
+        <v>3.3</v>
       </c>
       <c r="R214" t="n">
-        <v>2.9</v>
+        <v>4.01</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,22 +43699,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>1.63</v>
+        <v>2.22</v>
       </c>
       <c r="Q221" t="n">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
       <c r="R221" t="n">
-        <v>5.28</v>
+        <v>2.9</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="R223" t="n">
-        <v>2.05</v>
+        <v>4.17</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AF223" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="R224" t="n">
-        <v>4.17</v>
+        <v>2.05</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AF224" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="Q225" t="n">
-        <v>4.52</v>
+        <v>6.05</v>
       </c>
       <c r="R225" t="n">
-        <v>5.58</v>
+        <v>10</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AH225" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH230" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q231" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH231" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q232" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q233" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>2.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q243" t="n">
-        <v>3.35</v>
+        <v>5.27</v>
       </c>
       <c r="R243" t="n">
-        <v>2.31</v>
+        <v>1.39</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF245" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q255" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,22 +53943,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q287" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,22 +57686,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,22 +57883,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59853,22 +59853,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
           <t>Harbour View</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61439,7 +61439,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,22 +61823,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62414,7 +62414,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -62424,12 +62424,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,7 +62808,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q321" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R321" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63689,10 +63689,10 @@
         <v>0</v>
       </c>
       <c r="AE321" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF321" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG321" t="n">
         <v>0</v>
@@ -63793,7 +63793,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q322" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,10 +63886,10 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF322" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG322" t="n">
         <v>0</v>
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64581,7 +64581,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -64591,12 +64591,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -64778,7 +64778,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -64788,12 +64788,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -64975,7 +64975,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -64985,12 +64985,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -65763,7 +65763,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -65773,12 +65773,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -65811,13 +65811,13 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q332" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R332" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -65856,10 +65856,10 @@
         <v>0</v>
       </c>
       <c r="AE332" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF332" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG332" t="n">
         <v>0</v>
@@ -65960,7 +65960,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -65970,12 +65970,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -66008,13 +66008,13 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q333" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="R333" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="S333" t="n">
         <v>0</v>
@@ -66157,7 +66157,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -66167,12 +66167,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -66205,13 +66205,13 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q334" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R334" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -66250,10 +66250,10 @@
         <v>0</v>
       </c>
       <c r="AE334" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF334" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG334" t="n">
         <v>0</v>
@@ -66354,7 +66354,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -66364,12 +66364,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -66551,7 +66551,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -66561,12 +66561,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -66599,13 +66599,13 @@
         </is>
       </c>
       <c r="P336" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q336" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R336" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="S336" t="n">
         <v>0</v>
@@ -66945,7 +66945,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -66955,12 +66955,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -67142,7 +67142,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -67349,12 +67349,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -67536,7 +67536,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -67546,12 +67546,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G341" t="n">

--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>2.79</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="R6" t="n">
-        <v>2.79</v>
+        <v>4.33</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.37</v>
+        <v>3.44</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R73" t="n">
-        <v>2.91</v>
+        <v>2.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.44</v>
+        <v>2.37</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="R74" t="n">
-        <v>2.1</v>
+        <v>2.91</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.14</v>
+        <v>8.35</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.72</v>
+        <v>5.38</v>
       </c>
       <c r="R96" t="n">
-        <v>2.99</v>
+        <v>1.31</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19764,10 +19764,10 @@
         <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="R100" t="n">
-        <v>2.71</v>
+        <v>2.99</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>4.43</v>
+        <v>2.32</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.43</v>
+        <v>3.68</v>
       </c>
       <c r="R103" t="n">
-        <v>1.68</v>
+        <v>2.71</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20749,10 +20749,10 @@
         <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,116 +21482,116 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH107" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK107" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL107" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM107" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN107" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO107" t="n">
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR107" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS107" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU107" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV107" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW107" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX107" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY107" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ107" t="n">
         <v>0</v>
@@ -21600,19 +21600,19 @@
         <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE107" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF107" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,116 +21679,116 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK108" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN108" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO108" t="n">
         <v>0</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ108" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR108" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS108" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT108" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV108" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX108" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY108" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ108" t="n">
         <v>0</v>
@@ -21797,19 +21797,19 @@
         <v>0</v>
       </c>
       <c r="BB108" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC108" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD108" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE108" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.14</v>
+        <v>3.21</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="R112" t="n">
-        <v>3.35</v>
+        <v>2.01</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="R116" t="n">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="R117" t="n">
-        <v>2.39</v>
+        <v>2.85</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25225,7 +25225,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26604,17 +26604,17 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>3.19</v>
+        <v>1.59</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.72</v>
+        <v>3.32</v>
       </c>
       <c r="R146" t="n">
-        <v>2.31</v>
+        <v>5.9</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="Q149" t="n">
-        <v>2.9</v>
+        <v>3.79</v>
       </c>
       <c r="R149" t="n">
-        <v>3.6</v>
+        <v>4.95</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF181" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,22 +39956,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40350,22 +40350,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40547,22 +40547,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF213" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,22 +43699,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43896,22 +43896,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q222" t="n">
-        <v>4.88</v>
+        <v>3.78</v>
       </c>
       <c r="R222" t="n">
-        <v>7.06</v>
+        <v>2.05</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AF222" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.78</v>
+        <v>4.88</v>
       </c>
       <c r="R224" t="n">
-        <v>2.05</v>
+        <v>7.06</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AF224" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45571,10 +45571,10 @@
         <v>0</v>
       </c>
       <c r="AG229" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH229" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="Q232" t="n">
-        <v>3.48</v>
+        <v>4.52</v>
       </c>
       <c r="R232" t="n">
-        <v>3.43</v>
+        <v>5.58</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46162,10 +46162,10 @@
         <v>0</v>
       </c>
       <c r="AG232" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH232" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI232" t="n">
         <v>0</v>
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>9.300000000000001</v>
+        <v>2.23</v>
       </c>
       <c r="Q243" t="n">
-        <v>5.27</v>
+        <v>3.75</v>
       </c>
       <c r="R243" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q245" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF245" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -48914,10 +48914,10 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF246" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>3.61</v>
+        <v>2.49</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.51</v>
+        <v>3.21</v>
       </c>
       <c r="R253" t="n">
-        <v>2.06</v>
+        <v>3.04</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50687,10 +50687,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF255" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF257" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53943,22 +53943,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="Q282" t="n">
-        <v>3.53</v>
+        <v>4.98</v>
       </c>
       <c r="R282" t="n">
-        <v>2.54</v>
+        <v>5.99</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,16 +56006,16 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF282" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG282" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH282" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="Q283" t="n">
-        <v>4.98</v>
+        <v>3.53</v>
       </c>
       <c r="R283" t="n">
-        <v>5.99</v>
+        <v>2.54</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,16 +56203,16 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF283" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG283" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH283" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI283" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q286" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56794,10 +56794,10 @@
         <v>0</v>
       </c>
       <c r="AE286" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF286" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG286" t="n">
         <v>0</v>
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q287" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,22 +57686,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -57976,10 +57976,10 @@
         <v>0</v>
       </c>
       <c r="AE292" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF292" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG292" t="n">
         <v>0</v>
@@ -58080,22 +58080,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q294" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61035,22 +61035,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61439,7 +61439,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,22 +61823,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62035,7 +62035,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62414,7 +62414,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -62424,12 +62424,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63793,7 +63793,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q322" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R322" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,10 +63886,10 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF322" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG322" t="n">
         <v>0</v>
@@ -63990,7 +63990,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -64000,12 +64000,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -64038,13 +64038,13 @@
         </is>
       </c>
       <c r="P323" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q323" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R323" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S323" t="n">
         <v>0</v>
@@ -64083,10 +64083,10 @@
         <v>0</v>
       </c>
       <c r="AE323" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF323" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG323" t="n">
         <v>0</v>
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64591,12 +64591,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -64778,7 +64778,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -64788,12 +64788,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -64975,7 +64975,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -64985,12 +64985,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -65970,12 +65970,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -66157,7 +66157,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -66167,12 +66167,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -66205,13 +66205,13 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q334" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R334" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -66551,7 +66551,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -66561,12 +66561,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -66599,13 +66599,13 @@
         </is>
       </c>
       <c r="P336" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q336" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="R336" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="S336" t="n">
         <v>0</v>
@@ -66748,7 +66748,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -66758,12 +66758,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -67142,7 +67142,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -67349,12 +67349,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -67536,7 +67536,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -67546,12 +67546,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G341" t="n">

--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R5" t="n">
-        <v>2.91</v>
+        <v>4.33</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.44</v>
+        <v>2.37</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="R73" t="n">
-        <v>2.1</v>
+        <v>2.91</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.37</v>
+        <v>3.44</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R74" t="n">
-        <v>2.91</v>
+        <v>2.1</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19961,10 +19961,10 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="R103" t="n">
-        <v>2.71</v>
+        <v>3.13</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,116 +21482,116 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q107" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R107" t="n">
         <v>2.85</v>
       </c>
-      <c r="R107" t="n">
-        <v>3.18</v>
-      </c>
       <c r="S107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF107" t="n">
         <v>2.3</v>
       </c>
-      <c r="X107" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AG107" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ107" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO107" t="n">
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ107" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR107" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS107" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT107" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY107" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ107" t="n">
         <v>0</v>
@@ -21600,19 +21600,19 @@
         <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="R111" t="n">
-        <v>2.39</v>
+        <v>3.35</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,116 +22664,116 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI113" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK113" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL113" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM113" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN113" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO113" t="n">
         <v>0</v>
       </c>
       <c r="AP113" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR113" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS113" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU113" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV113" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW113" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX113" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY113" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ113" t="n">
         <v>0</v>
@@ -22782,19 +22782,19 @@
         <v>0</v>
       </c>
       <c r="BB113" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC113" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD113" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE113" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF113" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG113" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="R146" t="n">
-        <v>5.9</v>
+        <v>3.12</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.05</v>
+        <v>3.19</v>
       </c>
       <c r="Q147" t="n">
-        <v>2.9</v>
+        <v>3.72</v>
       </c>
       <c r="R147" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF147" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.79</v>
+        <v>3.32</v>
       </c>
       <c r="R149" t="n">
-        <v>4.95</v>
+        <v>5.9</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30402,10 +30402,10 @@
         <v>0</v>
       </c>
       <c r="AG152" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI152" t="n">
         <v>0</v>
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30599,10 +30599,10 @@
         <v>0</v>
       </c>
       <c r="AG153" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH153" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI153" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="R177" t="n">
-        <v>3.27</v>
+        <v>2.67</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="R179" t="n">
-        <v>2.67</v>
+        <v>3.27</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF181" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF182" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF184" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,22 +39956,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q202" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="R202" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40350,22 +40350,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q204" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,22 +43699,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="R222" t="n">
-        <v>2.05</v>
+        <v>4.17</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AF222" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.76</v>
+        <v>4.88</v>
       </c>
       <c r="R223" t="n">
-        <v>4.17</v>
+        <v>7.06</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.99</v>
+        <v>1.63</v>
       </c>
       <c r="AF223" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q224" t="n">
-        <v>4.88</v>
+        <v>3.78</v>
       </c>
       <c r="R224" t="n">
-        <v>7.06</v>
+        <v>2.05</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AF224" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q226" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q228" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45571,10 +45571,10 @@
         <v>0</v>
       </c>
       <c r="AG229" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH230" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF234" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q238" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -48914,10 +48914,10 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF246" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q252" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF252" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="Q255" t="n">
-        <v>3.56</v>
+        <v>3.21</v>
       </c>
       <c r="R255" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50687,10 +50687,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF255" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="R273" t="n">
-        <v>2.7</v>
+        <v>4.26</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54227,10 +54227,10 @@
         <v>0</v>
       </c>
       <c r="AC273" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54385,13 +54385,13 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q274" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R274" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S274" t="n">
         <v>0</v>
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q279" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55567,13 +55567,13 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q280" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R280" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q281" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55803,10 +55803,10 @@
         <v>0</v>
       </c>
       <c r="AC281" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD281" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE281" t="n">
         <v>0</v>
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="Q282" t="n">
-        <v>4.98</v>
+        <v>3.53</v>
       </c>
       <c r="R282" t="n">
-        <v>5.99</v>
+        <v>2.54</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,16 +56006,16 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF282" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG282" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH282" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.53</v>
+        <v>4.98</v>
       </c>
       <c r="R283" t="n">
-        <v>2.54</v>
+        <v>5.99</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,16 +56203,16 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG283" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH283" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q284" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56394,10 +56394,10 @@
         <v>0</v>
       </c>
       <c r="AC284" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD284" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF285" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q286" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57095,22 +57095,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57143,13 +57143,13 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q288" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R288" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S288" t="n">
         <v>0</v>
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,22 +57686,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q292" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -57976,10 +57976,10 @@
         <v>0</v>
       </c>
       <c r="AE292" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF292" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG292" t="n">
         <v>0</v>
@@ -58080,22 +58080,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>1.92</v>
+        <v>2.76</v>
       </c>
       <c r="Q294" t="n">
-        <v>3.52</v>
+        <v>2.72</v>
       </c>
       <c r="R294" t="n">
-        <v>4.22</v>
+        <v>2.63</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58364,10 +58364,10 @@
         <v>0</v>
       </c>
       <c r="AC294" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD294" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE294" t="n">
         <v>0</v>
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q295" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R295" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58561,10 +58561,10 @@
         <v>0</v>
       </c>
       <c r="AC295" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD295" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE295" t="n">
         <v>0</v>
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q297" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -58955,10 +58955,10 @@
         <v>0</v>
       </c>
       <c r="AC297" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD297" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59704,13 +59704,13 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q301" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R301" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S301" t="n">
         <v>0</v>
@@ -59743,10 +59743,10 @@
         <v>0</v>
       </c>
       <c r="AC301" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD301" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE301" t="n">
         <v>0</v>
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61035,22 +61035,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,22 +61823,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62217,22 +62217,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,22 +62414,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,7 +62808,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63053,13 +63053,13 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q318" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R318" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S318" t="n">
         <v>0</v>
@@ -63092,10 +63092,10 @@
         <v>0</v>
       </c>
       <c r="AC318" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD318" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE318" t="n">
         <v>0</v>
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63793,7 +63793,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q322" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,10 +63886,10 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF322" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG322" t="n">
         <v>0</v>
@@ -63990,7 +63990,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -64000,12 +64000,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -64038,13 +64038,13 @@
         </is>
       </c>
       <c r="P323" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q323" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R323" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S323" t="n">
         <v>0</v>
@@ -64083,10 +64083,10 @@
         <v>0</v>
       </c>
       <c r="AE323" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF323" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG323" t="n">
         <v>0</v>
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64235,13 +64235,13 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q324" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R324" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S324" t="n">
         <v>0</v>
@@ -64274,10 +64274,10 @@
         <v>0</v>
       </c>
       <c r="AC324" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD324" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE324" t="n">
         <v>0</v>
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64778,7 +64778,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -64788,12 +64788,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -65172,7 +65172,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -65182,12 +65182,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -65220,13 +65220,13 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q329" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R329" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S329" t="n">
         <v>0</v>
@@ -65265,10 +65265,10 @@
         <v>0</v>
       </c>
       <c r="AE329" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF329" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG329" t="n">
         <v>0</v>
@@ -65369,7 +65369,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -65379,12 +65379,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -65417,13 +65417,13 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q330" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R330" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S330" t="n">
         <v>0</v>
@@ -65462,10 +65462,10 @@
         <v>0</v>
       </c>
       <c r="AE330" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF330" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG330" t="n">
         <v>0</v>
@@ -65763,7 +65763,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -65773,12 +65773,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -65811,13 +65811,13 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q332" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R332" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -65856,10 +65856,10 @@
         <v>0</v>
       </c>
       <c r="AE332" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF332" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG332" t="n">
         <v>0</v>
@@ -65960,7 +65960,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -65970,12 +65970,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -66167,12 +66167,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -66205,13 +66205,13 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>1.39</v>
+        <v>3.36</v>
       </c>
       <c r="Q334" t="n">
-        <v>4.76</v>
+        <v>3.4</v>
       </c>
       <c r="R334" t="n">
-        <v>9.1</v>
+        <v>2.22</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -66250,10 +66250,10 @@
         <v>0</v>
       </c>
       <c r="AE334" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF334" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG334" t="n">
         <v>0</v>
@@ -66354,7 +66354,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -66364,12 +66364,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -66402,13 +66402,13 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q335" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R335" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="S335" t="n">
         <v>0</v>
@@ -66748,7 +66748,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -66758,12 +66758,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -67142,7 +67142,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -67349,12 +67349,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -67536,7 +67536,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -67546,12 +67546,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G341" t="n">

--- a/jogos_2026-04-26.xlsx
+++ b/jogos_2026-04-26.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>2.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>4.33</v>
+        <v>2.91</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.37</v>
+        <v>3.44</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R73" t="n">
-        <v>2.91</v>
+        <v>2.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.27</v>
+        <v>1.51</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.31</v>
+        <v>4.2</v>
       </c>
       <c r="R80" t="n">
-        <v>3.06</v>
+        <v>5.75</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.69</v>
+        <v>8.6</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="R88" t="n">
-        <v>4.38</v>
+        <v>1.27</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19567,10 +19567,10 @@
         <v>0</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="R98" t="n">
-        <v>4.35</v>
+        <v>2.71</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="R99" t="n">
-        <v>2.71</v>
+        <v>2.99</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19961,10 +19961,10 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="R107" t="n">
-        <v>2.85</v>
+        <v>2.39</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="R108" t="n">
-        <v>2.39</v>
+        <v>3.35</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,116 +21876,116 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL109" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN109" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO109" t="n">
         <v>0</v>
       </c>
       <c r="AP109" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR109" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS109" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AU109" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW109" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AY109" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ109" t="n">
         <v>0</v>
@@ -21994,19 +21994,19 @@
         <v>0</v>
       </c>
       <c r="BB109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF109" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG109" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,116 +22664,116 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.45</v>
+        <v>3.21</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="R113" t="n">
-        <v>3.18</v>
+        <v>2.01</v>
       </c>
       <c r="S113" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK113" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL113" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM113" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN113" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO113" t="n">
         <v>0</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AR113" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AS113" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AU113" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AV113" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW113" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AX113" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AY113" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ113" t="n">
         <v>0</v>
@@ -22782,19 +22782,19 @@
         <v>0</v>
       </c>
       <c r="BB113" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE113" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF113" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="R115" t="n">
-        <v>2.01</v>
+        <v>2.85</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -26998,17 +26998,17 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.27</v>
+        <v>1.59</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="R139" t="n">
-        <v>3.06</v>
+        <v>5.9</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q164" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q165" t="n">
-        <v>4.89</v>
+        <v>3.5</v>
       </c>
       <c r="R165" t="n">
-        <v>7.6</v>
+        <v>2.38</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="R177" t="n">
-        <v>2.67</v>
+        <v>3.27</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="R179" t="n">
-        <v>3.27</v>
+        <v>2.67</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.99</v>
+        <v>5.53</v>
       </c>
       <c r="R181" t="n">
-        <v>3.49</v>
+        <v>6.75</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF181" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="Q182" t="n">
-        <v>5.53</v>
+        <v>3.99</v>
       </c>
       <c r="R182" t="n">
-        <v>6.75</v>
+        <v>3.49</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF182" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.5</v>
+        <v>4.08</v>
       </c>
       <c r="R196" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39655,10 +39655,10 @@
         <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF199" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="Q202" t="n">
-        <v>3.56</v>
+        <v>4.12</v>
       </c>
       <c r="R202" t="n">
-        <v>2.86</v>
+        <v>5.28</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40547,22 +40547,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q204" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.38</v>
+        <v>3.97</v>
       </c>
       <c r="R205" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH225" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -45078,22 +45078,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH231" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Q232" t="n">
-        <v>4.52</v>
+        <v>3.48</v>
       </c>
       <c r="R232" t="n">
-        <v>5.58</v>
+        <v>3.43</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46162,10 +46162,10 @@
         <v>0</v>
       </c>
       <c r="AG232" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH232" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI232" t="n">
         <v>0</v>
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF234" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q237" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q244" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF245" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF252" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF253" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q260" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51672,10 +51672,10 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF260" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG260" t="n">
         <v>0</v>
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q262" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52066,10 +52066,10 @@
         <v>0</v>
       </c>
       <c r="AE262" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF262" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,13 +53006,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q267" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q272" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54227,10 +54227,10 @@
         <v>0</v>
       </c>
       <c r="AC273" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE273" t="n">
         <v>0</v>
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q276" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55015,10 +55015,10 @@
         <v>0</v>
       </c>
       <c r="AC277" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE277" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55567,13 +55567,13 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>2.78</v>
+        <v>2.27</v>
       </c>
       <c r="Q280" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="R280" t="n">
-        <v>2.66</v>
+        <v>3.36</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -55606,10 +55606,10 @@
         <v>0</v>
       </c>
       <c r="AC280" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD280" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE280" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="Q281" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="R281" t="n">
-        <v>3.36</v>
+        <v>2.66</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55803,10 +55803,10 @@
         <v>0</v>
       </c>
       <c r="AC281" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD281" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE281" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56394,10 +56394,10 @@
         <v>0</v>
       </c>
       <c r="AC284" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD284" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="R285" t="n">
-        <v>4.12</v>
+        <v>2.63</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56591,16 +56591,16 @@
         <v>0</v>
       </c>
       <c r="AC285" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD285" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE285" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF285" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="Q286" t="n">
-        <v>3.52</v>
+        <v>2.68</v>
       </c>
       <c r="R286" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56788,10 +56788,10 @@
         <v>0</v>
       </c>
       <c r="AC286" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD286" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE286" t="n">
         <v>0</v>
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57095,22 +57095,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57143,13 +57143,13 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q288" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S288" t="n">
         <v>0</v>
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57340,13 +57340,13 @@
         </is>
       </c>
       <c r="P289" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q289" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R289" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q293" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF293" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q294" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58364,10 +58364,10 @@
         <v>0</v>
       </c>
       <c r="AC294" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD294" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE294" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q295" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58561,10 +58561,10 @@
         <v>0</v>
       </c>
       <c r="AC295" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD295" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE295" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q297" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -58955,10 +58955,10 @@
         <v>0</v>
       </c>
       <c r="AC297" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD297" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59113,13 +59113,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q298" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R298" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -59152,10 +59152,10 @@
         <v>0</v>
       </c>
       <c r="AC298" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD298" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE298" t="n">
         <v>0</v>
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59507,13 +59507,13 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q300" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R300" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -59546,10 +59546,10 @@
         <v>0</v>
       </c>
       <c r="AC300" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD300" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE300" t="n">
         <v>0</v>
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59704,13 +59704,13 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q301" t="n">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="R301" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="S301" t="n">
         <v>0</v>
@@ -59743,10 +59743,10 @@
         <v>0</v>
       </c>
       <c r="AC301" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AD301" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE301" t="n">
         <v>0</v>
@@ -60247,22 +60247,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61439,7 +61439,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,22 +61823,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,22 +62414,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62659,13 +62659,13 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q316" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R316" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S316" t="n">
         <v>0</v>
@@ -62698,10 +62698,10 @@
         <v>0</v>
       </c>
       <c r="AC316" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD316" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE316" t="n">
         <v>0</v>
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63053,13 +63053,13 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q318" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S318" t="n">
         <v>0</v>
@@ -63092,10 +63092,10 @@
         <v>0</v>
       </c>
       <c r="AC318" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD318" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE318" t="n">
         <v>0</v>
@@ -63202,22 +63202,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q321" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63689,10 +63689,10 @@
         <v>0</v>
       </c>
       <c r="AE321" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF321" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG321" t="n">
         <v>0</v>
@@ -63793,7 +63793,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q322" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R322" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,10 +63886,10 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF322" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG322" t="n">
         <v>0</v>
@@ -64187,7 +64187,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -64197,12 +64197,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -64235,13 +64235,13 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q324" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R324" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S324" t="n">
         <v>0</v>
@@ -64274,10 +64274,10 @@
         <v>0</v>
       </c>
       <c r="AC324" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD324" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE324" t="n">
         <v>0</v>
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64432,13 +64432,13 @@
         </is>
       </c>
       <c r="P325" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q325" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S325" t="n">
         <v>0</v>
@@ -64477,10 +64477,10 @@
         <v>0</v>
       </c>
       <c r="AE325" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF325" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG325" t="n">
         <v>0</v>
@@ -64778,7 +64778,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -64788,12 +64788,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -64826,13 +64826,13 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q327" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R327" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S327" t="n">
         <v>0</v>
@@ -64865,10 +64865,10 @@
         <v>0</v>
       </c>
       <c r="AC327" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD327" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE327" t="n">
         <v>0</v>
@@ -65811,13 +65811,13 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q332" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R332" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -66157,7 +66157,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -66167,12 +66167,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -66205,13 +66205,13 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>3.36</v>
+        <v>2.02</v>
       </c>
       <c r="Q334" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="R334" t="n">
-        <v>2.22</v>
+        <v>3.94</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -66250,10 +66250,10 @@
         <v>0</v>
       </c>
       <c r="AE334" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AF334" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG334" t="n">
         <v>0</v>
@@ -66364,12 +66364,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -66402,13 +66402,13 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>1.39</v>
+        <v>3.36</v>
       </c>
       <c r="Q335" t="n">
-        <v>4.76</v>
+        <v>3.4</v>
       </c>
       <c r="R335" t="n">
-        <v>9.1</v>
+        <v>2.22</v>
       </c>
       <c r="S335" t="n">
         <v>0</v>
@@ -66447,10 +66447,10 @@
         <v>0</v>
       </c>
       <c r="AE335" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF335" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG335" t="n">
         <v>0</v>
@@ -66551,7 +66551,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -66561,12 +66561,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -66599,13 +66599,13 @@
         </is>
       </c>
       <c r="P336" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q336" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R336" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="S336" t="n">
         <v>0</v>
@@ -66748,7 +66748,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -66758,12 +66758,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -66796,13 +66796,13 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q337" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R337" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S337" t="n">
         <v>0</v>
@@ -66945,7 +66945,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -66955,12 +66955,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -67142,7 +67142,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -67349,12 +67349,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G340" t="n">
